--- a/results/Int Task Remove ACC -1.0/Rando_1_permute.xlsx
+++ b/results/Int Task Remove ACC -1.0/Rando_1_permute.xlsx
@@ -440,297 +440,297 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7972328645671223</v>
+        <v>0.8105884572215463</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7958612753836432</v>
+        <v>0.8141448553615724</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.8026703639776275</v>
+        <v>0.8210948567763598</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8026096224404138</v>
+        <v>0.8169408524565425</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.798708393461796</v>
+        <v>0.8099142638861379</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7757103647321808</v>
+        <v>0.8076589042000321</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.782605661035813</v>
+        <v>0.7990236080850381</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.7703728436282693</v>
+        <v>0.799205832696679</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.7768995406657047</v>
+        <v>0.8015787140526112</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.7739545193024155</v>
+        <v>0.7948950699376551</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.7711368288012979</v>
+        <v>0.7952947945257161</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.7726338624638049</v>
+        <v>0.7968682267055262</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.7675491167010932</v>
+        <v>0.8009556417003858</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.7853682691491468</v>
+        <v>0.7977891589560756</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.7915718287541382</v>
+        <v>0.7884642011638985</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.792441828659819</v>
+        <v>0.7935430991388661</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.7965449006347679</v>
+        <v>0.779315620195618</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.7853348801675109</v>
+        <v>0.779811361685672</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.7842826556501892</v>
+        <v>0.7778734802825802</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.7722829951991549</v>
+        <v>0.7810105354498552</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.7714326136781642</v>
+        <v>0.7768467219376928</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.7713816813332957</v>
+        <v>0.7547950916310613</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.7679801552493327</v>
+        <v>0.7547950916310613</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.7555786951887797</v>
+        <v>0.7523731643134037</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.7555786951887797</v>
+        <v>0.7420938852890411</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.758735368740745</v>
+        <v>0.7406772115484376</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.7790862360053949</v>
+        <v>0.7461460249191213</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.7772698376767305</v>
+        <v>0.7481289908793375</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.7796878035897872</v>
+        <v>0.7507350291917791</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.7791665959272989</v>
+        <v>0.7536153476132537</v>
       </c>
     </row>
     <row r="32">
@@ -740,587 +740,587 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.7791665959272989</v>
+        <v>0.7522848815822982</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.7616707695500033</v>
+        <v>0.7558922120671929</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.7765664054026014</v>
+        <v>0.7495122756383049</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.7736625071918357</v>
+        <v>0.7167757939315054</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.7536211954009979</v>
+        <v>0.7167757939315054</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.7602382501909963</v>
+        <v>0.716436810880658</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.763849542080492</v>
+        <v>0.7146556879167728</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.7661714910915556</v>
+        <v>0.7142814295011459</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.7601756222706394</v>
+        <v>0.7159312601982588</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.7516108768852041</v>
+        <v>0.7091417899889647</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.7475078049102553</v>
+        <v>0.6848347999962272</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.7503411523914623</v>
+        <v>0.7008650953095084</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.7591233977533177</v>
+        <v>0.6905701593050565</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.7719479735529083</v>
+        <v>0.6296294200315027</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.754424605981721</v>
+        <v>0.6230397177970818</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.762074266904351</v>
+        <v>0.6291355649245918</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.7589783348895994</v>
+        <v>0.6151725568980315</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.7389743734849985</v>
+        <v>0.6197204380181659</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.7389743734849985</v>
+        <v>0.6284791035907302</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.7345715552285825</v>
+        <v>0.5896682795242542</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.7070335681880346</v>
+        <v>0.5785131528064665</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.7072256019920207</v>
+        <v>0.5767476868226705</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.7079839280156193</v>
+        <v>0.5767476868226705</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.7147283136677891</v>
+        <v>0.5767476868226705</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.7155630382086906</v>
+        <v>0.5700014147873574</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.7156277411505051</v>
+        <v>0.5907852069833904</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.7148028258019486</v>
+        <v>0.5815326863039152</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.7160725502956906</v>
+        <v>0.5707263518293201</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.7070316818048914</v>
+        <v>0.5691940428020336</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.7081310659007951</v>
+        <v>0.5685768182375522</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.7179557265876273</v>
+        <v>0.5592948699810418</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.6882663195721683</v>
+        <v>0.5556071795742433</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.6877098365449006</v>
+        <v>0.5441640021504768</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.6768467219376928</v>
+        <v>0.544381502126897</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.7019020401233694</v>
+        <v>0.5453984512794394</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.6932099638757628</v>
+        <v>0.5659373909434745</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.6884074210312856</v>
+        <v>0.5659373909434745</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.6894243701838281</v>
+        <v>0.5675813738528432</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.6703688822236684</v>
+        <v>0.5473031323392095</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.6625566150740877</v>
+        <v>0.5486277505824207</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.6274080152419759</v>
+        <v>0.5486277505824207</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.6337722946907747</v>
+        <v>0.5586914160135065</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.6337722946907747</v>
+        <v>0.5598945511822906</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.6285090970827085</v>
+        <v>0.5543238731218698</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.6238906652330155</v>
+        <v>0.5522194240872264</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.5281623798609736</v>
+        <v>0.557582411363572</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.5502511719155277</v>
+        <v>0.5556503777482245</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.5414046008884864</v>
+        <v>0.5665076445676882</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.550659007951105</v>
+        <v>0.5630825386944343</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.5135314035633778</v>
+        <v>0.55522914839233</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.5136372296577159</v>
+        <v>0.5624223045942861</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.4980166567631552</v>
+        <v>0.5824185318279995</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.4935512105863822</v>
+        <v>0.5495999924544674</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.4834973543476415</v>
+        <v>0.5172824764437904</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.4878120785112664</v>
+        <v>0.4949741093913584</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.4995433066410118</v>
+        <v>0.5003527536477934</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.4995433066410118</v>
+        <v>0.4969433047546287</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.4988653405393169</v>
+        <v>0.4920858681606821</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.4924363581487036</v>
+        <v>0.4969629231393188</v>
       </c>
     </row>
   </sheetData>
